--- a/exports/DABUR_full_report.xlsx
+++ b/exports/DABUR_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,22 +557,22 @@
         <v>2.99</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44578.38541666666</v>
+        <v>44578.55208333334</v>
       </c>
       <c r="H2" t="n">
-        <v>571.65</v>
+        <v>570</v>
       </c>
       <c r="I2" t="n">
         <v>570.7764</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>7</v>
+        <v>7.166666666666667</v>
       </c>
       <c r="K2" t="n">
-        <v>-2.74</v>
+        <v>-3.02</v>
       </c>
       <c r="L2" t="n">
-        <v>2.96</v>
+        <v>3.2</v>
       </c>
       <c r="M2" t="n">
         <v>0.77</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>3.17</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>547.95</v>
+        <v>555.5</v>
       </c>
       <c r="I3" t="n">
         <v>550.3585837884652</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>15</v>
+        <v>15.83333333333333</v>
       </c>
       <c r="K3" t="n">
-        <v>3.87</v>
+        <v>2.54</v>
       </c>
       <c r="L3" t="n">
         <v>0.36</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>5.01</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44610.38541666666</v>
+        <v>44610.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>550</v>
+        <v>546.2</v>
       </c>
       <c r="I4" t="n">
         <v>549.2260471352768</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.99</v>
+        <v>-1.67</v>
       </c>
       <c r="L4" t="n">
         <v>1.8</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>4.6</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44620.38541666666</v>
+        <v>44620.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>544.9</v>
+        <v>564.6</v>
       </c>
       <c r="I5" t="n">
         <v>557.815571008202</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K5" t="n">
-        <v>0.24</v>
+        <v>-3.37</v>
       </c>
       <c r="L5" t="n">
-        <v>1.57</v>
+        <v>4.38</v>
       </c>
       <c r="M5" t="n">
         <v>0.49</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>7.3</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44624.55208333334</v>
+        <v>44627.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>538.5</v>
+        <v>505.85</v>
       </c>
       <c r="I6" t="n">
         <v>536.1203177222925</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K6" t="n">
-        <v>-4.62</v>
+        <v>-10.41</v>
       </c>
       <c r="L6" t="n">
-        <v>4.86</v>
+        <v>10.56</v>
       </c>
       <c r="M6" t="n">
-        <v>1.07</v>
+        <v>3.44</v>
       </c>
       <c r="N6" t="n">
-        <v>4.35</v>
+        <v>6.07</v>
       </c>
       <c r="O6" t="n">
         <v>3.5</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,22 +902,22 @@
         <v>9.84</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44630.38541666666</v>
+        <v>44630.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>540.75</v>
+        <v>543.9</v>
       </c>
       <c r="I7" t="n">
         <v>542.7394205881635</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.9</v>
+        <v>-7.52</v>
       </c>
       <c r="L7" t="n">
-        <v>7.34</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="M7" t="n">
         <v>2.27</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S7" t="b">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>6.98</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44642.55208333334</v>
+        <v>44643.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>535.3</v>
+        <v>524.3</v>
       </c>
       <c r="I8" t="n">
         <v>532.1269192843084</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>12</v>
+        <v>12.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.58</v>
+        <v>-3.6</v>
       </c>
       <c r="L8" t="n">
-        <v>2.32</v>
+        <v>3.93</v>
       </c>
       <c r="M8" t="n">
         <v>1.25</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>7.39</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44651.55208333334</v>
+        <v>44652.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>537.1</v>
+        <v>542.3</v>
       </c>
       <c r="I9" t="n">
         <v>540.4464869718247</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.44</v>
+        <v>-3.43</v>
       </c>
       <c r="L9" t="n">
-        <v>2.8</v>
+        <v>3.6</v>
       </c>
       <c r="M9" t="n">
         <v>0.6</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>5.02</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44683.55208333334</v>
+        <v>44685.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>557.45</v>
+        <v>540.15</v>
       </c>
       <c r="I10" t="n">
         <v>544.4335039632921</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K10" t="n">
-        <v>2.79</v>
+        <v>-0.4</v>
       </c>
       <c r="L10" t="n">
         <v>1.4</v>
@@ -1011,7 +1130,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N10" t="n">
-        <v>2.66</v>
+        <v>3.15</v>
       </c>
       <c r="O10" t="n">
         <v>1.47</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.31</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44712.38541666666</v>
+        <v>44712.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>511.65</v>
+        <v>523</v>
       </c>
       <c r="I11" t="n">
         <v>518.7600315765119</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>27</v>
+        <v>27.16666666666667</v>
       </c>
       <c r="K11" t="n">
-        <v>5.28</v>
+        <v>3.18</v>
       </c>
       <c r="L11" t="n">
         <v>4.57</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>5.89</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44719.55208333334</v>
+        <v>44720.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>501.5</v>
+        <v>493.25</v>
       </c>
       <c r="I12" t="n">
         <v>496.4163596342471</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>-4.11</v>
+        <v>-5.69</v>
       </c>
       <c r="L12" t="n">
-        <v>5.01</v>
+        <v>5.74</v>
       </c>
       <c r="M12" t="n">
         <v>1.22</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>5.69</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>509.95</v>
+        <v>515.5</v>
       </c>
       <c r="I13" t="n">
         <v>511.4707438940484</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K13" t="n">
-        <v>-3.39</v>
+        <v>-4.51</v>
       </c>
       <c r="L13" t="n">
-        <v>4.35</v>
+        <v>5.21</v>
       </c>
       <c r="M13" t="n">
-        <v>0.86</v>
+        <v>1.48</v>
       </c>
       <c r="N13" t="n">
         <v>3.22</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>4.83</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44798.55208333334</v>
+        <v>44799.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>578.8</v>
+        <v>570.5</v>
       </c>
       <c r="I14" t="n">
         <v>572.8537669016609</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K14" t="n">
-        <v>12.28</v>
+        <v>10.67</v>
       </c>
       <c r="L14" t="n">
         <v>4.55</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>4</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>5.38</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44825.55208333334</v>
+        <v>44826.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>560</v>
+        <v>573.15</v>
       </c>
       <c r="I15" t="n">
         <v>565.4299545325739</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K15" t="n">
-        <v>1.84</v>
+        <v>-0.46</v>
       </c>
       <c r="L15" t="n">
         <v>2.72</v>
@@ -1296,7 +1475,7 @@
         <v>1.37</v>
       </c>
       <c r="N15" t="n">
-        <v>1.85</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
         <v>-1.01</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>5.65</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>555</v>
+        <v>546.65</v>
       </c>
       <c r="I16" t="n">
         <v>550.925243207429</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.17</v>
+        <v>-4.62</v>
       </c>
       <c r="L16" t="n">
-        <v>3.66</v>
+        <v>4.65</v>
       </c>
       <c r="M16" t="n">
         <v>0.6899999999999999</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.14</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44859.55208333334</v>
+        <v>44861.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>532.5</v>
+        <v>547.9</v>
       </c>
       <c r="I17" t="n">
         <v>543.319570334893</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K17" t="n">
-        <v>2.59</v>
+        <v>-0.23</v>
       </c>
       <c r="L17" t="n">
         <v>1.98</v>
       </c>
       <c r="M17" t="n">
-        <v>0.97</v>
+        <v>1.69</v>
       </c>
       <c r="N17" t="n">
-        <v>3.25</v>
+        <v>3.47</v>
       </c>
       <c r="O17" t="n">
         <v>-1.71</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>4.96</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44911.38541666666</v>
+        <v>44911.55208333334</v>
       </c>
       <c r="H18" t="n">
-        <v>584.7</v>
+        <v>579</v>
       </c>
       <c r="I18" t="n">
         <v>581.16770012319</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>50</v>
+        <v>50.16666666666666</v>
       </c>
       <c r="K18" t="n">
-        <v>6.72</v>
+        <v>5.68</v>
       </c>
       <c r="L18" t="n">
         <v>2.17</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>4.14</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44945.55208333334</v>
+        <v>44946.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>555</v>
+        <v>564.75</v>
       </c>
       <c r="I19" t="n">
         <v>563.4226082526907</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K19" t="n">
-        <v>4.15</v>
+        <v>2.46</v>
       </c>
       <c r="L19" t="n">
         <v>1.87</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>4.94</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44959.55208333334</v>
+        <v>44960.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>555</v>
+        <v>530.5</v>
       </c>
       <c r="I20" t="n">
         <v>546.0758573224214</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.73</v>
+        <v>-6.06</v>
       </c>
       <c r="L20" t="n">
-        <v>3.23</v>
+        <v>6.46</v>
       </c>
       <c r="M20" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>1.39</v>
+        <v>3.81</v>
       </c>
       <c r="O20" t="n">
         <v>1.93</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>9.09</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45007.38541666666</v>
+        <v>45007.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>536.55</v>
+        <v>539.5</v>
       </c>
       <c r="I21" t="n">
         <v>538.1880267002279</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>47</v>
+        <v>47.16666666666666</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.14</v>
+        <v>-1.7</v>
       </c>
       <c r="L21" t="n">
         <v>5.94</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>3.58</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45022.38541666666</v>
+        <v>45022.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>529.9</v>
+        <v>526.6</v>
       </c>
       <c r="I22" t="n">
         <v>529.093534410272</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>14.83333333333333</v>
+        <v>15</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.78</v>
+        <v>-2.39</v>
       </c>
       <c r="L22" t="n">
-        <v>2.09</v>
+        <v>2.67</v>
       </c>
       <c r="M22" t="n">
         <v>0.57</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,22 +2006,22 @@
         <v>4.54</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45048.38541666666</v>
+        <v>45048.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>534.05</v>
+        <v>535.1</v>
       </c>
       <c r="I23" t="n">
         <v>535.0536364746785</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.41</v>
+        <v>-1.61</v>
       </c>
       <c r="L23" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="M23" t="n">
         <v>0.45</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>2.51</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45050.55208333334</v>
+        <v>45051.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>529.6</v>
+        <v>510.55</v>
       </c>
       <c r="I24" t="n">
         <v>524.5666963783303</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>2</v>
+        <v>2.833333333333333</v>
       </c>
       <c r="K24" t="n">
-        <v>-1.03</v>
+        <v>-4.59</v>
       </c>
       <c r="L24" t="n">
-        <v>1.29</v>
+        <v>5.06</v>
       </c>
       <c r="M24" t="n">
-        <v>-0</v>
+        <v>2.28</v>
       </c>
       <c r="N24" t="n">
-        <v>1.74</v>
+        <v>4.56</v>
       </c>
       <c r="O24" t="n">
         <v>0.39</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,28 +2144,28 @@
         <v>5.25</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45058.55208333334</v>
+        <v>45061.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>518.4</v>
+        <v>532</v>
       </c>
       <c r="I25" t="n">
         <v>528.7175105061775</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.54</v>
+        <v>-4.2</v>
       </c>
       <c r="L25" t="n">
-        <v>2.99</v>
+        <v>4.58</v>
       </c>
       <c r="M25" t="n">
         <v>0.5</v>
       </c>
       <c r="N25" t="n">
-        <v>1.84</v>
+        <v>2.85</v>
       </c>
       <c r="O25" t="n">
         <v>-4.56</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.6</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45114.38541666666</v>
+        <v>45114.55208333334</v>
       </c>
       <c r="H26" t="n">
-        <v>578.65</v>
+        <v>571.6</v>
       </c>
       <c r="I26" t="n">
         <v>571.6636500338103</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K26" t="n">
-        <v>8.77</v>
+        <v>7.44</v>
       </c>
       <c r="L26" t="n">
         <v>3.38</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>4.99</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45175.55208333334</v>
+        <v>45176.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>562</v>
+        <v>567</v>
       </c>
       <c r="I27" t="n">
         <v>566.9304899919289</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>61</v>
+        <v>61.83333333333334</v>
       </c>
       <c r="K27" t="n">
-        <v>1.68</v>
+        <v>0.8</v>
       </c>
       <c r="L27" t="n">
         <v>4.05</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>85</v>
+        <v>86</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>3</v>
+      </c>
+      <c r="U27" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>3.13</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45194.38541666666</v>
+        <v>45194.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>559.2</v>
+        <v>554.4</v>
       </c>
       <c r="I28" t="n">
         <v>555.2777822470415</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.38</v>
+        <v>-2.22</v>
       </c>
       <c r="L28" t="n">
-        <v>2.37</v>
+        <v>2.5</v>
       </c>
       <c r="M28" t="n">
         <v>0.22</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>3.67</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45232.38541666666</v>
+        <v>45232.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>524</v>
+        <v>533.25</v>
       </c>
       <c r="I29" t="n">
         <v>531.8701372583826</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>37.83333333333334</v>
+        <v>38</v>
       </c>
       <c r="K29" t="n">
-        <v>5.48</v>
+        <v>3.81</v>
       </c>
       <c r="L29" t="n">
         <v>1.38</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>3</v>
+      </c>
+      <c r="U29" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>5.14</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H30" t="n">
-        <v>540.8</v>
+        <v>535</v>
       </c>
       <c r="I30" t="n">
         <v>537.9527288885325</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>47.83333333333334</v>
+        <v>48</v>
       </c>
       <c r="K30" t="n">
-        <v>1.42</v>
+        <v>0.33</v>
       </c>
       <c r="L30" t="n">
         <v>3.1</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>3.79</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45288.55208333334</v>
+        <v>45289.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>544.8</v>
+        <v>555.2</v>
       </c>
       <c r="I31" t="n">
         <v>545.8241612820175</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>8.833333333333334</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.83</v>
+        <v>-3.78</v>
       </c>
       <c r="L31" t="n">
-        <v>2.01</v>
+        <v>4.67</v>
       </c>
       <c r="M31" t="n">
         <v>0.31</v>
       </c>
       <c r="N31" t="n">
-        <v>1.76</v>
+        <v>2.18</v>
       </c>
       <c r="O31" t="n">
         <v>-2.38</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>4.1</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45300.55208333334</v>
+        <v>45301.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>547.8</v>
+        <v>546.55</v>
       </c>
       <c r="I32" t="n">
         <v>547.2326496158861</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K32" t="n">
-        <v>-1.33</v>
+        <v>-1.56</v>
       </c>
       <c r="L32" t="n">
-        <v>2.08</v>
+        <v>2.32</v>
       </c>
       <c r="M32" t="n">
         <v>0.01</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>4.34</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45322.55208333334</v>
+        <v>45323.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>542</v>
+        <v>560.25</v>
       </c>
       <c r="I33" t="n">
         <v>548.925495985365</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K33" t="n">
-        <v>0.83</v>
+        <v>-2.51</v>
       </c>
       <c r="L33" t="n">
-        <v>2.81</v>
+        <v>5.3</v>
       </c>
       <c r="M33" t="n">
         <v>1.19</v>
       </c>
       <c r="N33" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="O33" t="n">
         <v>0.31</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>5.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45348.38541666666</v>
+        <v>45348.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>531.8</v>
+        <v>527</v>
       </c>
       <c r="I34" t="n">
         <v>531.54310868497</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>25</v>
+        <v>25.16666666666667</v>
       </c>
       <c r="K34" t="n">
-        <v>-5.08</v>
+        <v>-5.93</v>
       </c>
       <c r="L34" t="n">
-        <v>5.64</v>
+        <v>5.96</v>
       </c>
       <c r="M34" t="n">
         <v>0.55</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>3.73</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45407.55208333334</v>
+        <v>45408.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>505.7</v>
+        <v>510.25</v>
       </c>
       <c r="I35" t="n">
         <v>510.0279161680868</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>59</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>4.04</v>
+        <v>3.18</v>
       </c>
       <c r="L35" t="n">
         <v>3.41</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>4</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>3.16</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45516.38541666666</v>
+        <v>45516.55208333334</v>
       </c>
       <c r="H36" t="n">
-        <v>622</v>
+        <v>621.15</v>
       </c>
       <c r="I36" t="n">
         <v>621.2504814729248</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>108</v>
+        <v>108.1666666666667</v>
       </c>
       <c r="K36" t="n">
-        <v>21.9</v>
+        <v>21.73</v>
       </c>
       <c r="L36" t="n">
         <v>1</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>146</v>
+        <v>147</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>4.97</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45525.38541666666</v>
+        <v>45525.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>631.85</v>
+        <v>634.45</v>
       </c>
       <c r="I37" t="n">
         <v>633.6803397387079</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>8.833333333333334</v>
+        <v>9</v>
       </c>
       <c r="K37" t="n">
-        <v>-1.72</v>
+        <v>-2.14</v>
       </c>
       <c r="L37" t="n">
-        <v>1.76</v>
+        <v>2.38</v>
       </c>
       <c r="M37" t="n">
         <v>0.63</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,28 +3041,28 @@
         <v>4.28</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45559.55208333334</v>
+        <v>45560.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>655.5</v>
+        <v>626.45</v>
       </c>
       <c r="I38" t="n">
         <v>642.027101202109</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34</v>
+        <v>34.83333333333334</v>
       </c>
       <c r="K38" t="n">
-        <v>3.32</v>
+        <v>-1.26</v>
       </c>
       <c r="L38" t="n">
-        <v>0.58</v>
+        <v>1.94</v>
       </c>
       <c r="M38" t="n">
-        <v>0.32</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N38" t="n">
-        <v>1.53</v>
+        <v>4.29</v>
       </c>
       <c r="O38" t="n">
         <v>2.17</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>7.21</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45621.55208333334</v>
+        <v>45622.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>521.5</v>
+        <v>527.65</v>
       </c>
       <c r="I39" t="n">
         <v>526.6130178064465</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>61.16666666666666</v>
+        <v>62</v>
       </c>
       <c r="K39" t="n">
-        <v>16.75</v>
+        <v>15.77</v>
       </c>
       <c r="L39" t="n">
         <v>4.39</v>
@@ -2673,7 +3140,19 @@
         <v>1</v>
       </c>
       <c r="Q39" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>5.02</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45632.55208333334</v>
+        <v>45635.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>523.5</v>
+        <v>507.15</v>
       </c>
       <c r="I40" t="n">
         <v>507.8813153030358</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.79</v>
+        <v>-3.89</v>
       </c>
       <c r="L40" t="n">
-        <v>2.08</v>
+        <v>4.63</v>
       </c>
       <c r="M40" t="n">
         <v>1.42</v>
       </c>
       <c r="N40" t="n">
-        <v>0.42</v>
+        <v>3.17</v>
       </c>
       <c r="O40" t="n">
         <v>0.67</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,28 +3248,28 @@
         <v>5.61</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>513.8</v>
+        <v>524.6</v>
       </c>
       <c r="I41" t="n">
         <v>518.9784725137076</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K41" t="n">
-        <v>-1.31</v>
+        <v>-3.44</v>
       </c>
       <c r="L41" t="n">
-        <v>2.68</v>
+        <v>3.52</v>
       </c>
       <c r="M41" t="n">
         <v>0.4</v>
       </c>
       <c r="N41" t="n">
-        <v>1.54</v>
+        <v>1.99</v>
       </c>
       <c r="O41" t="n">
         <v>-3.17</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>4.18</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>524</v>
+        <v>509.2</v>
       </c>
       <c r="I42" t="n">
         <v>509.7576651679231</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>3</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.11</v>
+        <v>-2.94</v>
       </c>
       <c r="L42" t="n">
-        <v>2.01</v>
+        <v>4.48</v>
       </c>
       <c r="M42" t="n">
-        <v>-0</v>
+        <v>0.32</v>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O42" t="n">
         <v>1.99</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>4.81</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45673.55208333334</v>
+        <v>45674.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>523</v>
+        <v>529.5</v>
       </c>
       <c r="I43" t="n">
         <v>527.6237912139824</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>-2.71</v>
+        <v>-3.99</v>
       </c>
       <c r="L43" t="n">
-        <v>4.26</v>
+        <v>4.45</v>
       </c>
       <c r="M43" t="n">
         <v>0.58</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>0</v>
+      </c>
+      <c r="T43" t="n">
+        <v>1</v>
+      </c>
+      <c r="U43" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>5.32</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45706.55208333334</v>
+        <v>45707.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>515.3</v>
+        <v>507</v>
       </c>
       <c r="I44" t="n">
         <v>510.0514368735483</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.68</v>
+        <v>-4.25</v>
       </c>
       <c r="L44" t="n">
-        <v>2.93</v>
+        <v>4.38</v>
       </c>
       <c r="M44" t="n">
         <v>1.01</v>
       </c>
       <c r="N44" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="O44" t="n">
         <v>0.79</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>4.78</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45736.55208333334</v>
+        <v>45737.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>497.5</v>
+        <v>505.8</v>
       </c>
       <c r="I45" t="n">
         <v>503.2316714836924</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K45" t="n">
-        <v>1.87</v>
+        <v>0.24</v>
       </c>
       <c r="L45" t="n">
         <v>1.58</v>
@@ -3006,7 +3545,7 @@
         <v>0.72</v>
       </c>
       <c r="N45" t="n">
-        <v>1.5</v>
+        <v>2.06</v>
       </c>
       <c r="O45" t="n">
         <v>-2</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,28 +3593,28 @@
         <v>4.26</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45748.55208333334</v>
+        <v>45750.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>497.6</v>
+        <v>465.7</v>
       </c>
       <c r="I46" t="n">
         <v>496.431590009509</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K46" t="n">
-        <v>-1.62</v>
+        <v>-7.93</v>
       </c>
       <c r="L46" t="n">
-        <v>1.83</v>
+        <v>9.41</v>
       </c>
       <c r="M46" t="n">
-        <v>0.28</v>
+        <v>4.75</v>
       </c>
       <c r="N46" t="n">
-        <v>1.6</v>
+        <v>6.39</v>
       </c>
       <c r="O46" t="n">
         <v>2.06</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>7.41</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>473.85</v>
+        <v>481.25</v>
       </c>
       <c r="I47" t="n">
         <v>475.2718561344686</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K47" t="n">
-        <v>-1.75</v>
+        <v>-3.34</v>
       </c>
       <c r="L47" t="n">
         <v>3.88</v>
@@ -3129,7 +3692,19 @@
         <v>1</v>
       </c>
       <c r="Q47" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,28 +3731,28 @@
         <v>6.09</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45784.55208333334</v>
+        <v>45785.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>480</v>
+        <v>469.25</v>
       </c>
       <c r="I48" t="n">
         <v>472.5881744865931</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.26</v>
+        <v>-2.49</v>
       </c>
       <c r="L48" t="n">
-        <v>1.65</v>
+        <v>4.19</v>
       </c>
       <c r="M48" t="n">
-        <v>1.56</v>
+        <v>2.09</v>
       </c>
       <c r="N48" t="n">
-        <v>1.34</v>
+        <v>2.65</v>
       </c>
       <c r="O48" t="n">
         <v>1.51</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>4.84</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45793.55208333334</v>
+        <v>45796.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>476.65</v>
+        <v>482.7</v>
       </c>
       <c r="I49" t="n">
         <v>482.1388854151623</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>11</v>
       </c>
       <c r="K49" t="n">
-        <v>-1.58</v>
+        <v>-2.87</v>
       </c>
       <c r="L49" t="n">
-        <v>2.12</v>
+        <v>3.16</v>
       </c>
       <c r="M49" t="n">
         <v>1.09</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,28 +3869,28 @@
         <v>4.34</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45819.55208333334</v>
+        <v>45820.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>486.05</v>
+        <v>475.9</v>
       </c>
       <c r="I50" t="n">
         <v>478.7708256669455</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>0.6899999999999999</v>
+        <v>-1.41</v>
       </c>
       <c r="L50" t="n">
-        <v>1.6</v>
+        <v>1.74</v>
       </c>
       <c r="M50" t="n">
         <v>0.1</v>
       </c>
       <c r="N50" t="n">
-        <v>1.28</v>
+        <v>2.58</v>
       </c>
       <c r="O50" t="n">
         <v>1.33</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,25 +3938,25 @@
         <v>4.42</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45833.55208333334</v>
+        <v>45834.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>480</v>
+        <v>480.4</v>
       </c>
       <c r="I51" t="n">
         <v>480.1242601545284</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.86</v>
+        <v>-0.95</v>
       </c>
       <c r="L51" t="n">
         <v>2.5</v>
       </c>
       <c r="M51" t="n">
-        <v>0.22</v>
+        <v>0.42</v>
       </c>
       <c r="N51" t="n">
         <v>1.65</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>2.62</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45862.55208333334</v>
+        <v>45863.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>512.65</v>
+        <v>511.1</v>
       </c>
       <c r="I52" t="n">
         <v>511.5936785139563</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K52" t="n">
-        <v>6.71</v>
+        <v>6.39</v>
       </c>
       <c r="L52" t="n">
         <v>0.33</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>2.98</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45868.55208333334</v>
+        <v>45869.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>520.8</v>
+        <v>528</v>
       </c>
       <c r="I53" t="n">
         <v>525.6507964822605</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K53" t="n">
-        <v>-1.9</v>
+        <v>-3.31</v>
       </c>
       <c r="L53" t="n">
-        <v>2.84</v>
+        <v>3.8</v>
       </c>
       <c r="M53" t="n">
         <v>0.31</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>4.47</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>526</v>
+        <v>515.55</v>
       </c>
       <c r="I54" t="n">
         <v>517.3302785824532</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.38</v>
+        <v>-2.36</v>
       </c>
       <c r="L54" t="n">
-        <v>2.05</v>
+        <v>2.51</v>
       </c>
       <c r="M54" t="n">
         <v>0.48</v>
       </c>
       <c r="N54" t="n">
-        <v>1.18</v>
+        <v>2.47</v>
       </c>
       <c r="O54" t="n">
         <v>1.61</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>5.29</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>501.15</v>
+        <v>524.9</v>
       </c>
       <c r="I55" t="n">
         <v>519.2876890588776</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K55" t="n">
-        <v>2.79</v>
+        <v>-1.81</v>
       </c>
       <c r="L55" t="n">
-        <v>1.67</v>
+        <v>2.76</v>
       </c>
       <c r="M55" t="n">
-        <v>0.26</v>
+        <v>2.54</v>
       </c>
       <c r="N55" t="n">
-        <v>0.9</v>
+        <v>3.65</v>
       </c>
       <c r="O55" t="n">
         <v>-2.47</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.58</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45919.55208333334</v>
+        <v>45922.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>535.7</v>
+        <v>531.75</v>
       </c>
       <c r="I56" t="n">
         <v>532.1687656049168</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K56" t="n">
-        <v>2.06</v>
+        <v>1.31</v>
       </c>
       <c r="L56" t="n">
         <v>2.9</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="57">
@@ -3669,19 +4352,19 @@
         <v>3.69</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45946.55208333334</v>
+        <v>45947.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>500.05</v>
+        <v>509.3</v>
       </c>
       <c r="I57" t="n">
         <v>503.2450867193762</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>5.96</v>
+        <v>4.22</v>
       </c>
       <c r="L57" t="n">
         <v>0.9399999999999999</v>
@@ -3690,7 +4373,7 @@
         <v>0.48</v>
       </c>
       <c r="N57" t="n">
-        <v>1.41</v>
+        <v>1.61</v>
       </c>
       <c r="O57" t="n">
         <v>-3.02</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,28 +4421,28 @@
         <v>4.29</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45960.55208333334</v>
+        <v>45961.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>500.5</v>
+        <v>488.9</v>
       </c>
       <c r="I58" t="n">
         <v>494.5654920436615</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>-1.73</v>
+        <v>-4.01</v>
       </c>
       <c r="L58" t="n">
-        <v>2.14</v>
+        <v>4.17</v>
       </c>
       <c r="M58" t="n">
         <v>0.06</v>
       </c>
       <c r="N58" t="n">
-        <v>1.57</v>
+        <v>2.48</v>
       </c>
       <c r="O58" t="n">
         <v>1.61</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>5.71</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45964.55208333334</v>
+        <v>45965.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>502.3</v>
+        <v>517.25</v>
       </c>
       <c r="I59" t="n">
         <v>508.5359374205017</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K59" t="n">
-        <v>-2.74</v>
+        <v>-5.8</v>
       </c>
       <c r="L59" t="n">
-        <v>3.18</v>
+        <v>6.35</v>
       </c>
       <c r="M59" t="n">
         <v>0.48</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>6.25</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45994.38541666666</v>
+        <v>45994.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>506.9</v>
+        <v>504.8</v>
       </c>
       <c r="I60" t="n">
         <v>505.7517977917299</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K60" t="n">
-        <v>-2</v>
+        <v>-2.41</v>
       </c>
       <c r="L60" t="n">
         <v>3.18</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>3.6</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46021.55208333334</v>
+        <v>46022.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>495</v>
+        <v>505.85</v>
       </c>
       <c r="I61" t="n">
         <v>500.3384564808808</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>1.94</v>
+        <v>-0.21</v>
       </c>
       <c r="L61" t="n">
         <v>1.21</v>
@@ -3918,7 +4649,7 @@
         <v>0.3</v>
       </c>
       <c r="N61" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="O61" t="n">
         <v>-0.43</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>3.94</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46050.55208333334</v>
+        <v>46051.38541666666</v>
       </c>
       <c r="H62" t="n">
-        <v>517.2</v>
+        <v>503.2</v>
       </c>
       <c r="I62" t="n">
         <v>504.4307685906965</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>29</v>
       </c>
       <c r="K62" t="n">
-        <v>2.24</v>
+        <v>-0.52</v>
       </c>
       <c r="L62" t="n">
         <v>2.16</v>
@@ -3975,7 +4718,7 @@
         <v>1.17</v>
       </c>
       <c r="N62" t="n">
-        <v>1.4</v>
+        <v>1.69</v>
       </c>
       <c r="O62" t="n">
         <v>1.45</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>6.4</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46122.38541666666</v>
+        <v>46122.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>432.65</v>
+        <v>437</v>
       </c>
       <c r="I63" t="n">
         <v>432.9714908989705</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>71</v>
+        <v>71.16666666666667</v>
       </c>
       <c r="K63" t="n">
-        <v>14.02</v>
+        <v>13.16</v>
       </c>
       <c r="L63" t="n">
         <v>4.43</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>5.94</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46157.55208333334</v>
+        <v>46160.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>467.1</v>
+        <v>455.8</v>
       </c>
       <c r="I64" t="n">
         <v>462.9597783942414</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>35</v>
+        <v>37.83333333333334</v>
       </c>
       <c r="K64" t="n">
-        <v>6.89</v>
+        <v>4.3</v>
       </c>
       <c r="L64" t="n">
         <v>3.28</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>6.71</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46203.55208333334</v>
+        <v>46204.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>422.1</v>
+        <v>442.85</v>
       </c>
       <c r="I65" t="n">
         <v>434.1079924365159</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K65" t="n">
-        <v>7.39</v>
+        <v>2.84</v>
       </c>
       <c r="L65" t="n">
         <v>2.41</v>
@@ -4146,7 +4925,7 @@
         <v>1.41</v>
       </c>
       <c r="N65" t="n">
-        <v>1.75</v>
+        <v>5.51</v>
       </c>
       <c r="O65" t="n">
         <v>-2.37</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>3</v>
+      </c>
+      <c r="U65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>6.4</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46217.38541666666</v>
+        <v>46217.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>435.2</v>
+        <v>432.85</v>
       </c>
       <c r="I66" t="n">
         <v>433.9699141516958</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>-1.73</v>
+        <v>-2.26</v>
       </c>
       <c r="L66" t="n">
         <v>4.56</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>4.74</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46276.55208333334</v>
+        <v>46280.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>376</v>
+        <v>387.75</v>
       </c>
       <c r="I67" t="n">
         <v>381.6134132093774</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>59</v>
+        <v>62.83333333333334</v>
       </c>
       <c r="K67" t="n">
-        <v>13.13</v>
+        <v>10.42</v>
       </c>
       <c r="L67" t="n">
         <v>1.19</v>
@@ -4260,7 +5063,7 @@
         <v>1.13</v>
       </c>
       <c r="N67" t="n">
-        <v>2.06</v>
+        <v>2.37</v>
       </c>
       <c r="O67" t="n">
         <v>-1.45</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>4.77</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46295.55208333334</v>
+        <v>46296.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>381.65</v>
+        <v>377.9</v>
       </c>
       <c r="I68" t="n">
         <v>378.0347836513583</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K68" t="n">
-        <v>-1.57</v>
+        <v>-2.54</v>
       </c>
       <c r="L68" t="n">
-        <v>2.84</v>
+        <v>2.89</v>
       </c>
       <c r="M68" t="n">
         <v>1</v>
       </c>
       <c r="N68" t="n">
-        <v>1.27</v>
+        <v>1.45</v>
       </c>
       <c r="O68" t="n">
         <v>2.37</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,14 @@
       <c r="Q69" t="n">
         <v>36</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7314,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.7</v>
+        <v>25.7</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7324,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7334,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>108</v>
+        <v>108.2</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7344,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7354,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32.2</v>
+        <v>33.9</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7364,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55.4</v>
+        <v>55.8</v>
       </c>
     </row>
     <row r="11">
@@ -6569,7 +7404,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.4</v>
+        <v>-0.46</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7414,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.98</v>
+        <v>-0.96</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7424,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.84</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7434,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21.9</v>
+        <v>21.73</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7444,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>44.8</v>
+        <v>29.9</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7454,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2.72</v>
+        <v>3.59</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7464,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2.41</v>
+        <v>3.38</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7474,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>7.34</v>
+        <v>10.56</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7484,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7494,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7504,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.82</v>
+        <v>1.03</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7514,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.66</v>
+        <v>4.75</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7524,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>2.14</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7534,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4.35</v>
+        <v>6.39</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7544,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29">
